--- a/Result/profitability/8354.xlsx
+++ b/Result/profitability/8354.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1125</v>
+        <v>0.25875</v>
       </c>
       <c r="N2" t="n">
-        <v>14.2275</v>
+        <v>15.145</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -684,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>0.175</v>
+        <v>0.26</v>
       </c>
       <c r="N3" t="n">
-        <v>14.34375</v>
+        <v>15.57125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.13125</v>
+        <v>0.2625</v>
       </c>
       <c r="N4" t="n">
-        <v>14.39</v>
+        <v>15.18625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05125000000000002</v>
+        <v>0.34125</v>
       </c>
       <c r="N5" t="n">
-        <v>13.21875</v>
+        <v>14.2775</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>0.175</v>
+        <v>0.2175</v>
       </c>
       <c r="N6" t="n">
-        <v>12.12125</v>
+        <v>13.5975</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05125000000000002</v>
+        <v>0.11625</v>
       </c>
       <c r="N7" t="n">
-        <v>12.21125</v>
+        <v>13.40625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.01124999999999998</v>
+        <v>0.08750000000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>12.8575</v>
+        <v>13.49125</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.03999999999999997</v>
+        <v>-0.03999999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>12.3175</v>
@@ -1645,7 +1645,7 @@
         <v>-0.19</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.08124999999999998</v>
+        <v>-0.08124999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>11.765</v>
@@ -2026,7 +2026,7 @@
         <v>0.01</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.04499999999999998</v>
+        <v>-0.045</v>
       </c>
       <c r="N13" t="n">
         <v>12.7025</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8354</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>169</v>
+      </c>
+      <c r="D75" t="n">
+        <v>131</v>
+      </c>
+      <c r="E75" t="n">
+        <v>37</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>103</v>
+      </c>
+      <c r="J75" t="n">
+        <v>105</v>
+      </c>
+      <c r="K75" t="n">
+        <v>86</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.23125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.633333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.069999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2980599647266311</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.886178861788618</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.469999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6223365172667157</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
